--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Unicaja.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Unicaja.xlsx
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>40.7703</v>
+        <v>35.3708</v>
       </c>
       <c r="E2" t="n">
-        <v>35.8314</v>
+        <v>32.6596</v>
       </c>
       <c r="F2" t="n">
-        <v>4.938699999999999</v>
+        <v>2.711500000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>21.2421</v>
+        <v>22.3824</v>
       </c>
       <c r="H2" t="n">
-        <v>5.8221</v>
+        <v>8.722899999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>15.4203</v>
+        <v>13.6593</v>
       </c>
       <c r="J2" t="n">
-        <v>40.7532</v>
+        <v>48.4344</v>
       </c>
       <c r="K2" t="n">
-        <v>13.0124</v>
+        <v>17.7468</v>
       </c>
       <c r="L2" t="n">
-        <v>27.7409</v>
+        <v>30.6878</v>
       </c>
       <c r="M2" t="n">
-        <v>-19.5112</v>
+        <v>-26.052</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.1905</v>
+        <v>-9.0244</v>
       </c>
       <c r="O2" t="n">
-        <v>-12.3206</v>
+        <v>-17.0282</v>
       </c>
       <c r="P2" t="n">
-        <v>21.776</v>
+        <v>17.7553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-15.6516</v>
+        <v>-26.4056</v>
       </c>
       <c r="R2" t="n">
-        <v>37.4276</v>
+        <v>44.1608</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.047699999999999</v>
+        <v>-5.4776</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.2108</v>
+        <v>-8.2926</v>
       </c>
       <c r="U2" t="n">
-        <v>1.163</v>
+        <v>2.8149</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7995</v>
+        <v>0.7108999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>15.9404</v>
+        <v>18.9231</v>
       </c>
       <c r="X2" t="n">
-        <v>-14.1406</v>
+        <v>-18.2122</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>35.9737</v>
+        <v>33.8056</v>
       </c>
       <c r="E3" t="n">
-        <v>18.3771</v>
+        <v>39.8051</v>
       </c>
       <c r="F3" t="n">
-        <v>17.5969</v>
+        <v>-5.9994</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.8986</v>
+        <v>16.3442</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.1627</v>
+        <v>19.3971</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2638</v>
+        <v>-3.0524</v>
       </c>
       <c r="J3" t="n">
-        <v>7.5057</v>
+        <v>46.5197</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3356</v>
+        <v>35.2173</v>
       </c>
       <c r="L3" t="n">
-        <v>5.170300000000001</v>
+        <v>11.3024</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.404399999999999</v>
+        <v>-30.1751</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.4981</v>
+        <v>-15.8203</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.9064</v>
+        <v>-14.3549</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>-3.8699</v>
       </c>
       <c r="Q3" t="n">
-        <v>-21.549</v>
+        <v>-53.2658</v>
       </c>
       <c r="R3" t="n">
-        <v>22.0029</v>
+        <v>49.3963</v>
       </c>
       <c r="S3" t="n">
-        <v>35.76</v>
+        <v>15.4619</v>
       </c>
       <c r="T3" t="n">
-        <v>20.497</v>
+        <v>10.0067</v>
       </c>
       <c r="U3" t="n">
-        <v>15.2635</v>
+        <v>5.4554</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6583</v>
+        <v>5.8693</v>
       </c>
       <c r="W3" t="n">
-        <v>11.9235</v>
+        <v>36.5451</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.2651</v>
+        <v>-30.6757</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>25.0374</v>
+        <v>32.266</v>
       </c>
       <c r="E4" t="n">
-        <v>26.6389</v>
+        <v>16.3517</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.601300000000001</v>
+        <v>15.9145</v>
       </c>
       <c r="G4" t="n">
-        <v>13.2564</v>
+        <v>-4.855000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>13.9989</v>
+        <v>-5.4925</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7420999999999994</v>
+        <v>0.6380000000000006</v>
       </c>
       <c r="J4" t="n">
-        <v>38.61</v>
+        <v>7.807700000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>26.8765</v>
+        <v>2.547600000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>11.7332</v>
+        <v>5.2601</v>
       </c>
       <c r="M4" t="n">
-        <v>-25.3534</v>
+        <v>-12.6625</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.8784</v>
+        <v>-8.040099999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.4751</v>
+        <v>-4.6223</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.7635</v>
+        <v>1.3659</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47.1812</v>
+        <v>-22.9907</v>
       </c>
       <c r="R4" t="n">
-        <v>42.418</v>
+        <v>24.3568</v>
       </c>
       <c r="S4" t="n">
-        <v>7.7826</v>
+        <v>35.5798</v>
       </c>
       <c r="T4" t="n">
-        <v>3.7782</v>
+        <v>19.5207</v>
       </c>
       <c r="U4" t="n">
-        <v>4.0047</v>
+        <v>16.0592</v>
       </c>
       <c r="V4" t="n">
-        <v>8.761699999999999</v>
+        <v>0.1751000000000005</v>
       </c>
       <c r="W4" t="n">
-        <v>31.432</v>
+        <v>12.014</v>
       </c>
       <c r="X4" t="n">
-        <v>-22.6702</v>
+        <v>-11.839</v>
       </c>
     </row>
     <row r="5">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>15.8721</v>
+        <v>22.2276</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3408</v>
+        <v>25.2757</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5312</v>
+        <v>-3.047800000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>30.4757</v>
+        <v>42.4991</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.768800000000001</v>
+        <v>-7.457399999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>36.2443</v>
+        <v>49.9559</v>
       </c>
       <c r="J5" t="n">
-        <v>59.2636</v>
+        <v>78.2252</v>
       </c>
       <c r="K5" t="n">
-        <v>12.5887</v>
+        <v>13.9811</v>
       </c>
       <c r="L5" t="n">
-        <v>46.6748</v>
+        <v>64.2443</v>
       </c>
       <c r="M5" t="n">
-        <v>-28.7881</v>
+        <v>-35.7264</v>
       </c>
       <c r="N5" t="n">
-        <v>-18.3579</v>
+        <v>-21.4379</v>
       </c>
       <c r="O5" t="n">
-        <v>-10.4304</v>
+        <v>-14.2883</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.2681</v>
+        <v>-6.6012</v>
       </c>
       <c r="Q5" t="n">
-        <v>-48.5424</v>
+        <v>-63.737</v>
       </c>
       <c r="R5" t="n">
-        <v>46.2742</v>
+        <v>57.136</v>
       </c>
       <c r="S5" t="n">
-        <v>-20.3051</v>
+        <v>-21.9357</v>
       </c>
       <c r="T5" t="n">
-        <v>-17.9134</v>
+        <v>-19.6761</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.3916</v>
+        <v>-2.258999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>7.97</v>
+        <v>8.2658</v>
       </c>
       <c r="W5" t="n">
-        <v>21.5326</v>
+        <v>30.4635</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.5626</v>
+        <v>-22.198</v>
       </c>
     </row>
     <row r="6">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>13.0628</v>
+        <v>8.7461</v>
       </c>
       <c r="E6" t="n">
-        <v>16.8323</v>
+        <v>15.3457</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.7694</v>
+        <v>-6.600000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>12.0282</v>
+        <v>6.903300000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.492</v>
+        <v>0.08250000000000013</v>
       </c>
       <c r="I6" t="n">
-        <v>11.5362</v>
+        <v>6.821</v>
       </c>
       <c r="J6" t="n">
-        <v>17.7693</v>
+        <v>18.4919</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7253</v>
+        <v>6.579499999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>14.0441</v>
+        <v>11.9125</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.7412</v>
+        <v>-11.5883</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.2335</v>
+        <v>-6.4967</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.5078</v>
+        <v>-5.0916</v>
       </c>
       <c r="P6" t="n">
-        <v>4.536700000000001</v>
+        <v>5.4633</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8147</v>
+        <v>-4.5527</v>
       </c>
       <c r="R6" t="n">
-        <v>6.3512</v>
+        <v>10.0157</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.5084</v>
+        <v>-5.7396</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.4933</v>
+        <v>-6.1478</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.01519999999999994</v>
+        <v>0.4085</v>
       </c>
       <c r="V6" t="n">
-        <v>0.006399999999999989</v>
+        <v>2.1189</v>
       </c>
       <c r="W6" t="n">
-        <v>4.3707</v>
+        <v>7.555</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.364199999999999</v>
+        <v>-5.436</v>
       </c>
     </row>
     <row r="7">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>8.680099999999999</v>
+        <v>7.604900000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>17.1063</v>
+        <v>16.5008</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.426299999999999</v>
+        <v>-8.8956</v>
       </c>
       <c r="G7" t="n">
-        <v>24.3866</v>
+        <v>22.9056</v>
       </c>
       <c r="H7" t="n">
-        <v>12.8406</v>
+        <v>12.0133</v>
       </c>
       <c r="I7" t="n">
-        <v>11.5455</v>
+        <v>10.8924</v>
       </c>
       <c r="J7" t="n">
-        <v>42.9056</v>
+        <v>42.6931</v>
       </c>
       <c r="K7" t="n">
-        <v>19.4499</v>
+        <v>18.8936</v>
       </c>
       <c r="L7" t="n">
-        <v>23.456</v>
+        <v>23.7993</v>
       </c>
       <c r="M7" t="n">
-        <v>-18.5192</v>
+        <v>-19.7877</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.6091</v>
+        <v>-6.880500000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-11.9102</v>
+        <v>-12.9073</v>
       </c>
       <c r="P7" t="n">
-        <v>-15.6514</v>
+        <v>-15.0238</v>
       </c>
       <c r="Q7" t="n">
-        <v>-47.6351</v>
+        <v>-47.8028</v>
       </c>
       <c r="R7" t="n">
-        <v>31.9834</v>
+        <v>32.779</v>
       </c>
       <c r="S7" t="n">
-        <v>-14.6901</v>
+        <v>-14.4942</v>
       </c>
       <c r="T7" t="n">
-        <v>-14.8013</v>
+        <v>-14.5151</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1113999999999999</v>
+        <v>0.02119999999999986</v>
       </c>
       <c r="V7" t="n">
-        <v>14.6353</v>
+        <v>14.2175</v>
       </c>
       <c r="W7" t="n">
-        <v>36.6368</v>
+        <v>36.1252</v>
       </c>
       <c r="X7" t="n">
-        <v>-22.0016</v>
+        <v>-21.9078</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BUTAJEVAS</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5395</v>
+        <v>2.920100000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0051</v>
+        <v>16.7343</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5344</v>
+        <v>-13.8138</v>
       </c>
       <c r="G8" t="n">
-        <v>0.861</v>
+        <v>-5.398699999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4718</v>
+        <v>-2.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3892</v>
+        <v>-3.3376</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0746</v>
+        <v>9.614600000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4.022400000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>5.5921</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7864</v>
+        <v>-15.0133</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4718</v>
+        <v>-6.0834</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3145</v>
+        <v>-8.9298</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5.463200000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-13.4302</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>18.8934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3215</v>
+        <v>7.8729</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>5.1097</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2519</v>
+        <v>2.7632</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-5.0172</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>15.4401</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-20.4571</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. TRUJILLO</t>
+          <t>A. BUTAJEVAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5458</v>
+        <v>0.5413</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3654</v>
+        <v>0.0048</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1804</v>
+        <v>0.5365</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0385</v>
+        <v>0.8641</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1371</v>
+        <v>0.4738</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.3903</v>
       </c>
       <c r="J9" t="n">
-        <v>0.052</v>
+        <v>0.0745</v>
       </c>
       <c r="K9" t="n">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.7896</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
-        <v>-0.09039999999999999</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.1891</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.09859999999999999</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.9073</v>
-      </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4927</v>
+        <v>-0.3228</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7168</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2241</v>
+        <v>-0.2531</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>M. TRUJILLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.849000000000001</v>
+        <v>-1.539</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7078</v>
+        <v>-0.3665</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.5569</v>
+        <v>-1.1725</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.317400000000001</v>
+        <v>-0.0337</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.532699999999999</v>
+        <v>-0.1351</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7847</v>
+        <v>0.1014</v>
       </c>
       <c r="J10" t="n">
-        <v>14.0246</v>
+        <v>0.0517</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2645</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
-        <v>8.760400000000001</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-20.342</v>
+        <v>-0.0854</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.7969</v>
+        <v>-0.1868</v>
       </c>
       <c r="O10" t="n">
-        <v>-12.5451</v>
+        <v>0.1014</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2683</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-28.581</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>30.8493</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>26.9777</v>
+        <v>0.4947</v>
       </c>
       <c r="T10" t="n">
-        <v>16.592</v>
+        <v>0.7199</v>
       </c>
       <c r="U10" t="n">
-        <v>10.3852</v>
+        <v>-0.2252</v>
       </c>
       <c r="V10" t="n">
-        <v>-24.7776</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6719</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-26.4496</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. KRAVISH</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.875299999999999</v>
+        <v>-1.891999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.203799999999999</v>
+        <v>4.299399999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3282</v>
+        <v>-6.191</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7715999999999998</v>
+        <v>-6.377699999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4194</v>
+        <v>-0.1283000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6478000000000003</v>
+        <v>-6.249499999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6164000000000005</v>
+        <v>16.4735</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03289999999999993</v>
+        <v>7.797400000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5834999999999999</v>
+        <v>8.676299999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3881</v>
+        <v>-22.8511</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4522</v>
+        <v>-7.925300000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06420000000000003</v>
+        <v>-14.9256</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>2.2763</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.763500000000001</v>
+        <v>-30.0474</v>
       </c>
       <c r="R11" t="n">
-        <v>5.2172</v>
+        <v>32.3237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02749999999999997</v>
+        <v>27.8688</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1493</v>
+        <v>17.0396</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1218</v>
+        <v>10.8291</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5298</v>
+        <v>-25.6593</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>0.8337000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6225</v>
+        <v>-26.4927</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.081300000000001</v>
+        <v>-8.014799999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>9.914199999999999</v>
+        <v>-8.927299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.9954</v>
+        <v>0.9128000000000006</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.134599999999999</v>
+        <v>-33.7958</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.202</v>
+        <v>-8.773300000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9324999999999996</v>
+        <v>-25.0227</v>
       </c>
       <c r="J12" t="n">
-        <v>6.0551</v>
+        <v>0.01709999999999867</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9576999999999996</v>
+        <v>8.3635</v>
       </c>
       <c r="L12" t="n">
-        <v>7.0128</v>
+        <v>-8.346499999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.1894</v>
+        <v>-33.8128</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.2442</v>
+        <v>-17.1364</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.9453</v>
+        <v>-16.676</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1756</v>
+        <v>17.3001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.022</v>
+        <v>-19.121</v>
       </c>
       <c r="R12" t="n">
-        <v>15.1977</v>
+        <v>36.4212</v>
       </c>
       <c r="S12" t="n">
-        <v>6.4472</v>
+        <v>9.2926</v>
       </c>
       <c r="T12" t="n">
-        <v>4.4398</v>
+        <v>0.7291000000000006</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0071</v>
+        <v>8.563800000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.569899999999999</v>
+        <v>-0.8113999999999997</v>
       </c>
       <c r="W12" t="n">
-        <v>11.4413</v>
+        <v>9.4483</v>
       </c>
       <c r="X12" t="n">
-        <v>-16.0111</v>
+        <v>-10.2597</v>
       </c>
     </row>
     <row r="13">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.328000000000001</v>
+        <v>-10.6382</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.0594</v>
+        <v>-13.8912</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7312000000000003</v>
+        <v>3.252799999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7094</v>
+        <v>-5.4259</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8731000000000004</v>
+        <v>-10.5419</v>
       </c>
       <c r="I13" t="n">
-        <v>1.836399999999999</v>
+        <v>5.1155</v>
       </c>
       <c r="J13" t="n">
-        <v>21.6421</v>
+        <v>19.2398</v>
       </c>
       <c r="K13" t="n">
-        <v>11.6857</v>
+        <v>3.7987</v>
       </c>
       <c r="L13" t="n">
-        <v>9.956299999999999</v>
+        <v>15.4412</v>
       </c>
       <c r="M13" t="n">
-        <v>-18.9327</v>
+        <v>-24.6656</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.8128</v>
+        <v>-14.3401</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.120000000000001</v>
+        <v>-10.3253</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.133999999999999</v>
+        <v>-2.276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-39.9228</v>
+        <v>-50.7618</v>
       </c>
       <c r="R13" t="n">
-        <v>38.7887</v>
+        <v>48.486</v>
       </c>
       <c r="S13" t="n">
-        <v>4.0525</v>
+        <v>7.159699999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.3619</v>
+        <v>-3.3283</v>
       </c>
       <c r="U13" t="n">
-        <v>9.4145</v>
+        <v>10.488</v>
       </c>
       <c r="V13" t="n">
-        <v>-11.9553</v>
+        <v>-10.0954</v>
       </c>
       <c r="W13" t="n">
-        <v>16.5832</v>
+        <v>20.9592</v>
       </c>
       <c r="X13" t="n">
-        <v>-28.5386</v>
+        <v>-31.0545</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>X. CASTANEDA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.5236</v>
+        <v>-17.5988</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.8233</v>
+        <v>-16.3469</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7004000000000008</v>
+        <v>-1.252</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.3915</v>
+        <v>-12.0653</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.3133</v>
+        <v>-7.1912</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.078199999999999</v>
+        <v>-4.8741</v>
       </c>
       <c r="J14" t="n">
-        <v>1.650399999999999</v>
+        <v>-8.0282</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4817</v>
+        <v>-5.1073</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1685999999999996</v>
+        <v>-2.9208</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.042</v>
+        <v>-4.0369</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.7951</v>
+        <v>-2.0838</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.2467</v>
+        <v>-1.9532</v>
       </c>
       <c r="P14" t="n">
-        <v>4.763400000000001</v>
+        <v>-5.2355</v>
       </c>
       <c r="Q14" t="n">
-        <v>-20.4149</v>
+        <v>-8.4224</v>
       </c>
       <c r="R14" t="n">
-        <v>25.1783</v>
+        <v>3.1869</v>
       </c>
       <c r="S14" t="n">
-        <v>7.6514</v>
+        <v>-1.459</v>
       </c>
       <c r="T14" t="n">
-        <v>6.723700000000001</v>
+        <v>-1.1435</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9278</v>
+        <v>-0.3156</v>
       </c>
       <c r="V14" t="n">
-        <v>-12.547</v>
+        <v>1.1608</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2177</v>
+        <v>1.2472</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.7648</v>
+        <v>-0.08640000000000003</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.7469</v>
+        <v>-17.7618</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.3686</v>
+        <v>-13.2561</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.3782</v>
+        <v>-4.5055</v>
       </c>
       <c r="G15" t="n">
-        <v>-26.8155</v>
+        <v>-18.184</v>
       </c>
       <c r="H15" t="n">
-        <v>-11.3367</v>
+        <v>-10.0905</v>
       </c>
       <c r="I15" t="n">
-        <v>-15.479</v>
+        <v>-8.0936</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3373000000000002</v>
+        <v>-1.691499999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7033</v>
+        <v>-2.4398</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.3656</v>
+        <v>0.7479000000000005</v>
       </c>
       <c r="M15" t="n">
-        <v>-27.1531</v>
+        <v>-16.4925</v>
       </c>
       <c r="N15" t="n">
-        <v>-15.0398</v>
+        <v>-7.651</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.1135</v>
+        <v>-8.841699999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>14.5173</v>
+        <v>3.869699999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14.9709</v>
+        <v>-23.9013</v>
       </c>
       <c r="R15" t="n">
-        <v>29.4882</v>
+        <v>27.771</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5778</v>
+        <v>11.147</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.7814</v>
+        <v>10.1429</v>
       </c>
       <c r="U15" t="n">
-        <v>3.3592</v>
+        <v>1.0045</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.0261</v>
+        <v>-14.5943</v>
       </c>
       <c r="W15" t="n">
-        <v>5.0461</v>
+        <v>2.1938</v>
       </c>
       <c r="X15" t="n">
-        <v>-10.0724</v>
+        <v>-16.7881</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X. CASTANEDA</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-17.5683</v>
+        <v>-21.4609</v>
       </c>
       <c r="E16" t="n">
-        <v>-16.2434</v>
+        <v>-23.2179</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3248</v>
+        <v>1.7572</v>
       </c>
       <c r="G16" t="n">
-        <v>-12.0526</v>
+        <v>-8.103199999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-7.18</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.8727</v>
+        <v>-16.2133</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.9609</v>
+        <v>11.0903</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.0685</v>
+        <v>16.2375</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.8924</v>
+        <v>-5.147600000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.0918</v>
+        <v>-19.1932</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1115</v>
+        <v>-8.127700000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9803</v>
+        <v>-11.0655</v>
       </c>
       <c r="P16" t="n">
-        <v>-5.2171</v>
+        <v>-5.2356</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8.392799999999999</v>
+        <v>-37.7869</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1757</v>
+        <v>32.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4553</v>
+        <v>-4.4879</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1433</v>
+        <v>-5.1955</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3121</v>
+        <v>0.7077999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1568</v>
+        <v>-3.6344</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>8.674300000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.09660000000000002</v>
+        <v>-12.3087</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>D. KRAVISH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>-20.5219</v>
+        <v>-24.4456</v>
       </c>
       <c r="E17" t="n">
-        <v>-20.6259</v>
+        <v>-23.0436</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1037000000000001</v>
+        <v>-1.4021</v>
       </c>
       <c r="G17" t="n">
-        <v>-8.263599999999999</v>
+        <v>-15.1452</v>
       </c>
       <c r="H17" t="n">
-        <v>6.810099999999999</v>
+        <v>-7.1365</v>
       </c>
       <c r="I17" t="n">
-        <v>-15.0736</v>
+        <v>-8.0084</v>
       </c>
       <c r="J17" t="n">
-        <v>11.5865</v>
+        <v>-6.8368</v>
       </c>
       <c r="K17" t="n">
-        <v>15.9782</v>
+        <v>-4.4734</v>
       </c>
       <c r="L17" t="n">
-        <v>-4.3916</v>
+        <v>-2.3634</v>
       </c>
       <c r="M17" t="n">
-        <v>-19.8502</v>
+        <v>-8.308299999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-9.168100000000001</v>
+        <v>-2.6632</v>
       </c>
       <c r="O17" t="n">
-        <v>-10.682</v>
+        <v>-5.6451</v>
       </c>
       <c r="P17" t="n">
-        <v>-5.444100000000001</v>
+        <v>-8.194700000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-36.5201</v>
+        <v>-20.0316</v>
       </c>
       <c r="R17" t="n">
-        <v>31.0761</v>
+        <v>11.8369</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.5818</v>
+        <v>2.977300000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-4.2733</v>
+        <v>0.7859</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6913000000000001</v>
+        <v>2.1913</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.2328</v>
+        <v>-4.0829</v>
       </c>
       <c r="W17" t="n">
-        <v>8.581300000000001</v>
+        <v>3.0393</v>
       </c>
       <c r="X17" t="n">
-        <v>-11.8141</v>
+        <v>-7.1221</v>
       </c>
     </row>
     <row r="18">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-24.3037</v>
+        <v>-26.8477</v>
       </c>
       <c r="E18" t="n">
-        <v>-16.4086</v>
+        <v>-12.4629</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.894600000000001</v>
+        <v>-14.3851</v>
       </c>
       <c r="G18" t="n">
-        <v>-10.0649</v>
+        <v>-7.7577</v>
       </c>
       <c r="H18" t="n">
-        <v>0.387</v>
+        <v>-3.0763</v>
       </c>
       <c r="I18" t="n">
-        <v>-10.4518</v>
+        <v>-4.681300000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>2.720100000000001</v>
+        <v>10.5593</v>
       </c>
       <c r="K18" t="n">
-        <v>7.138</v>
+        <v>6.658199999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.418100000000001</v>
+        <v>3.901</v>
       </c>
       <c r="M18" t="n">
-        <v>-12.7849</v>
+        <v>-18.3172</v>
       </c>
       <c r="N18" t="n">
-        <v>-6.7511</v>
+        <v>-9.734999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.0338</v>
+        <v>-8.5822</v>
       </c>
       <c r="P18" t="n">
-        <v>4.3098</v>
+        <v>2.7316</v>
       </c>
       <c r="Q18" t="n">
-        <v>-15.4248</v>
+        <v>-23.6739</v>
       </c>
       <c r="R18" t="n">
-        <v>19.7347</v>
+        <v>26.4057</v>
       </c>
       <c r="S18" t="n">
-        <v>-5.410600000000001</v>
+        <v>-3.9114</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.1221</v>
+        <v>-1.0839</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2885</v>
+        <v>-2.8276</v>
       </c>
       <c r="V18" t="n">
-        <v>-13.1378</v>
+        <v>-17.9099</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4178999999999999</v>
+        <v>1.7354</v>
       </c>
       <c r="X18" t="n">
-        <v>-13.5558</v>
+        <v>-19.6456</v>
       </c>
     </row>
     <row r="19">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>-24.7719</v>
+        <v>-39.9562</v>
       </c>
       <c r="E19" t="n">
-        <v>-11.8276</v>
+        <v>-23.9947</v>
       </c>
       <c r="F19" t="n">
-        <v>-12.944</v>
+        <v>-15.9615</v>
       </c>
       <c r="G19" t="n">
-        <v>-18.5209</v>
+        <v>-30.7421</v>
       </c>
       <c r="H19" t="n">
-        <v>-12.2239</v>
+        <v>-14.9937</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.296899999999999</v>
+        <v>-15.7485</v>
       </c>
       <c r="J19" t="n">
-        <v>4.299799999999999</v>
+        <v>-1.380600000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0395</v>
+        <v>-0.3115000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>3.2599</v>
+        <v>-1.0688</v>
       </c>
       <c r="M19" t="n">
-        <v>-22.8207</v>
+        <v>-29.3616</v>
       </c>
       <c r="N19" t="n">
-        <v>-13.264</v>
+        <v>-14.6824</v>
       </c>
       <c r="O19" t="n">
-        <v>-9.556899999999999</v>
+        <v>-14.6792</v>
       </c>
       <c r="P19" t="n">
-        <v>14.2905</v>
+        <v>12.7473</v>
       </c>
       <c r="Q19" t="n">
-        <v>-24.4981</v>
+        <v>-32.0963</v>
       </c>
       <c r="R19" t="n">
-        <v>38.7885</v>
+        <v>44.8436</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.01180000000000003</v>
+        <v>1.0704</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.789</v>
+        <v>-1.4275</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7773000000000001</v>
+        <v>2.4981</v>
       </c>
       <c r="V19" t="n">
-        <v>-20.5295</v>
+        <v>-23.0319</v>
       </c>
       <c r="W19" t="n">
-        <v>9.1593</v>
+        <v>10.9096</v>
       </c>
       <c r="X19" t="n">
-        <v>-29.6888</v>
+        <v>-33.9415</v>
       </c>
     </row>
     <row r="20">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>11.82020000000001</v>
+        <v>-26.67260000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>44.8279</v>
+        <v>31.47000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-33.0074</v>
+        <v>-58.14100000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>1.689700000000009</v>
+        <v>-35.9856</v>
       </c>
       <c r="H20" t="n">
-        <v>-13.581</v>
+        <v>-28.2782</v>
       </c>
       <c r="I20" t="n">
-        <v>15.2706</v>
+        <v>-7.707599999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>261.9054</v>
+        <v>291.3557</v>
       </c>
       <c r="K20" t="n">
-        <v>118.338</v>
+        <v>129.5633</v>
       </c>
       <c r="L20" t="n">
-        <v>143.5677</v>
+        <v>161.7923</v>
       </c>
       <c r="M20" t="n">
-        <v>-260.2164</v>
+        <v>-327.3403</v>
       </c>
       <c r="N20" t="n">
-        <v>-131.9205</v>
+        <v>-157.8412</v>
       </c>
       <c r="O20" t="n">
-        <v>-128.2968</v>
+        <v>-169.4989</v>
       </c>
       <c r="P20" t="n">
-        <v>35.1595</v>
+        <v>21.6255</v>
       </c>
       <c r="Q20" t="n">
-        <v>-389.0191</v>
+        <v>-479.1656</v>
       </c>
       <c r="R20" t="n">
-        <v>424.1785</v>
+        <v>500.7921</v>
       </c>
       <c r="S20" t="n">
-        <v>37.38209999999999</v>
+        <v>61.0969</v>
       </c>
       <c r="T20" t="n">
-        <v>-7.361199999999998</v>
+        <v>3.174499999999998</v>
       </c>
       <c r="U20" t="n">
-        <v>44.7434</v>
+        <v>57.92450000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-62.41049999999999</v>
+        <v>-73.4079</v>
       </c>
       <c r="W20" t="n">
-        <v>179.3008</v>
+        <v>216.1068</v>
       </c>
       <c r="X20" t="n">
-        <v>-241.7113</v>
+        <v>-289.5146</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Unicaja.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Unicaja.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>35.3708</v>
+        <v>45.4468</v>
       </c>
       <c r="E2" t="n">
-        <v>32.6596</v>
+        <v>41.7683</v>
       </c>
       <c r="F2" t="n">
-        <v>2.711500000000001</v>
+        <v>3.679</v>
       </c>
       <c r="G2" t="n">
-        <v>22.3824</v>
+        <v>42.4991</v>
       </c>
       <c r="H2" t="n">
-        <v>8.722899999999999</v>
+        <v>-7.457399999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>13.6593</v>
+        <v>49.9559</v>
       </c>
       <c r="J2" t="n">
-        <v>48.4344</v>
+        <v>78.2252</v>
       </c>
       <c r="K2" t="n">
-        <v>17.7468</v>
+        <v>13.9811</v>
       </c>
       <c r="L2" t="n">
-        <v>30.6878</v>
+        <v>64.2443</v>
       </c>
       <c r="M2" t="n">
-        <v>-26.052</v>
+        <v>-35.7264</v>
       </c>
       <c r="N2" t="n">
-        <v>-9.0244</v>
+        <v>-21.4379</v>
       </c>
       <c r="O2" t="n">
-        <v>-17.0282</v>
+        <v>-14.2883</v>
       </c>
       <c r="P2" t="n">
-        <v>17.7553</v>
+        <v>-6.6012</v>
       </c>
       <c r="Q2" t="n">
-        <v>-26.4056</v>
+        <v>-63.737</v>
       </c>
       <c r="R2" t="n">
-        <v>44.1608</v>
+        <v>57.136</v>
       </c>
       <c r="S2" t="n">
-        <v>-5.4776</v>
+        <v>1.2838</v>
       </c>
       <c r="T2" t="n">
-        <v>-8.2926</v>
+        <v>-3.1839</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8149</v>
+        <v>4.4673</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7108999999999999</v>
+        <v>8.2658</v>
       </c>
       <c r="W2" t="n">
-        <v>18.9231</v>
+        <v>30.4635</v>
       </c>
       <c r="X2" t="n">
-        <v>-18.2122</v>
+        <v>-22.198</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>33.8056</v>
+        <v>45.3702</v>
       </c>
       <c r="E3" t="n">
-        <v>39.8051</v>
+        <v>39.8915</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.9994</v>
+        <v>5.4785</v>
       </c>
       <c r="G3" t="n">
-        <v>16.3442</v>
+        <v>22.3824</v>
       </c>
       <c r="H3" t="n">
-        <v>19.3971</v>
+        <v>8.722899999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.0524</v>
+        <v>13.6593</v>
       </c>
       <c r="J3" t="n">
-        <v>46.5197</v>
+        <v>48.4344</v>
       </c>
       <c r="K3" t="n">
-        <v>35.2173</v>
+        <v>17.7468</v>
       </c>
       <c r="L3" t="n">
-        <v>11.3024</v>
+        <v>30.6878</v>
       </c>
       <c r="M3" t="n">
-        <v>-30.1751</v>
+        <v>-26.052</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.8203</v>
+        <v>-9.0244</v>
       </c>
       <c r="O3" t="n">
-        <v>-14.3549</v>
+        <v>-17.0282</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.8699</v>
+        <v>17.7553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-53.2658</v>
+        <v>-26.4056</v>
       </c>
       <c r="R3" t="n">
-        <v>49.3963</v>
+        <v>44.1608</v>
       </c>
       <c r="S3" t="n">
-        <v>15.4619</v>
+        <v>4.5217</v>
       </c>
       <c r="T3" t="n">
-        <v>10.0067</v>
+        <v>-1.06</v>
       </c>
       <c r="U3" t="n">
-        <v>5.4554</v>
+        <v>5.5818</v>
       </c>
       <c r="V3" t="n">
-        <v>5.8693</v>
+        <v>0.7108999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>36.5451</v>
+        <v>18.9231</v>
       </c>
       <c r="X3" t="n">
-        <v>-30.6757</v>
+        <v>-18.2122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>32.266</v>
+        <v>30.7783</v>
       </c>
       <c r="E4" t="n">
-        <v>16.3517</v>
+        <v>33.3469</v>
       </c>
       <c r="F4" t="n">
-        <v>15.9145</v>
+        <v>-2.5684</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.855000000000001</v>
+        <v>16.3442</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.4925</v>
+        <v>19.3971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6380000000000006</v>
+        <v>-3.0524</v>
       </c>
       <c r="J4" t="n">
-        <v>7.807700000000001</v>
+        <v>46.5197</v>
       </c>
       <c r="K4" t="n">
-        <v>2.547600000000001</v>
+        <v>35.2173</v>
       </c>
       <c r="L4" t="n">
-        <v>5.2601</v>
+        <v>11.3024</v>
       </c>
       <c r="M4" t="n">
-        <v>-12.6625</v>
+        <v>-30.1751</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.040099999999999</v>
+        <v>-15.8203</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.6223</v>
+        <v>-14.3549</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3659</v>
+        <v>-3.8699</v>
       </c>
       <c r="Q4" t="n">
-        <v>-22.9907</v>
+        <v>-53.2658</v>
       </c>
       <c r="R4" t="n">
-        <v>24.3568</v>
+        <v>49.3963</v>
       </c>
       <c r="S4" t="n">
-        <v>35.5798</v>
+        <v>12.4343</v>
       </c>
       <c r="T4" t="n">
-        <v>19.5207</v>
+        <v>3.548</v>
       </c>
       <c r="U4" t="n">
-        <v>16.0592</v>
+        <v>8.886100000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1751000000000005</v>
+        <v>5.8693</v>
       </c>
       <c r="W4" t="n">
-        <v>12.014</v>
+        <v>36.5451</v>
       </c>
       <c r="X4" t="n">
-        <v>-11.839</v>
+        <v>-30.6757</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>22.2276</v>
+        <v>19.1557</v>
       </c>
       <c r="E5" t="n">
-        <v>25.2757</v>
+        <v>25.3495</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.047800000000001</v>
+        <v>-6.194000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>42.4991</v>
+        <v>22.9056</v>
       </c>
       <c r="H5" t="n">
-        <v>-7.457399999999999</v>
+        <v>12.0133</v>
       </c>
       <c r="I5" t="n">
-        <v>49.9559</v>
+        <v>10.8924</v>
       </c>
       <c r="J5" t="n">
-        <v>78.2252</v>
+        <v>42.6931</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9811</v>
+        <v>18.8936</v>
       </c>
       <c r="L5" t="n">
-        <v>64.2443</v>
+        <v>23.7993</v>
       </c>
       <c r="M5" t="n">
-        <v>-35.7264</v>
+        <v>-19.7877</v>
       </c>
       <c r="N5" t="n">
-        <v>-21.4379</v>
+        <v>-6.880500000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-14.2883</v>
+        <v>-12.9073</v>
       </c>
       <c r="P5" t="n">
-        <v>-6.6012</v>
+        <v>-15.0238</v>
       </c>
       <c r="Q5" t="n">
-        <v>-63.737</v>
+        <v>-47.8028</v>
       </c>
       <c r="R5" t="n">
-        <v>57.136</v>
+        <v>32.779</v>
       </c>
       <c r="S5" t="n">
-        <v>-21.9357</v>
+        <v>-2.9432</v>
       </c>
       <c r="T5" t="n">
-        <v>-19.6761</v>
+        <v>-5.6664</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.258999999999999</v>
+        <v>2.7233</v>
       </c>
       <c r="V5" t="n">
-        <v>8.2658</v>
+        <v>14.2175</v>
       </c>
       <c r="W5" t="n">
-        <v>30.4635</v>
+        <v>36.1252</v>
       </c>
       <c r="X5" t="n">
-        <v>-22.198</v>
+        <v>-21.9078</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>8.7461</v>
+        <v>13.7616</v>
       </c>
       <c r="E6" t="n">
-        <v>15.3457</v>
+        <v>19.5126</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.600000000000001</v>
+        <v>-5.7509</v>
       </c>
       <c r="G6" t="n">
         <v>6.903300000000001</v>
@@ -922,13 +922,13 @@
         <v>10.0157</v>
       </c>
       <c r="S6" t="n">
-        <v>-5.7396</v>
+        <v>-0.7237</v>
       </c>
       <c r="T6" t="n">
-        <v>-6.1478</v>
+        <v>-1.9815</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4085</v>
+        <v>1.2578</v>
       </c>
       <c r="V6" t="n">
         <v>2.1189</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>7.604900000000002</v>
+        <v>12.9964</v>
       </c>
       <c r="E7" t="n">
-        <v>16.5008</v>
+        <v>2.437700000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.8956</v>
+        <v>10.5584</v>
       </c>
       <c r="G7" t="n">
-        <v>22.9056</v>
+        <v>-4.855000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>12.0133</v>
+        <v>-5.4925</v>
       </c>
       <c r="I7" t="n">
-        <v>10.8924</v>
+        <v>0.6380000000000006</v>
       </c>
       <c r="J7" t="n">
-        <v>42.6931</v>
+        <v>7.807700000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>18.8936</v>
+        <v>2.547600000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>23.7993</v>
+        <v>5.2601</v>
       </c>
       <c r="M7" t="n">
-        <v>-19.7877</v>
+        <v>-12.6625</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.880500000000001</v>
+        <v>-8.040099999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-12.9073</v>
+        <v>-4.6223</v>
       </c>
       <c r="P7" t="n">
-        <v>-15.0238</v>
+        <v>1.3659</v>
       </c>
       <c r="Q7" t="n">
-        <v>-47.8028</v>
+        <v>-22.9907</v>
       </c>
       <c r="R7" t="n">
-        <v>32.779</v>
+        <v>24.3568</v>
       </c>
       <c r="S7" t="n">
-        <v>-14.4942</v>
+        <v>16.31</v>
       </c>
       <c r="T7" t="n">
-        <v>-14.5151</v>
+        <v>5.6069</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02119999999999986</v>
+        <v>10.7034</v>
       </c>
       <c r="V7" t="n">
-        <v>14.2175</v>
+        <v>0.1751000000000005</v>
       </c>
       <c r="W7" t="n">
-        <v>36.1252</v>
+        <v>12.014</v>
       </c>
       <c r="X7" t="n">
-        <v>-21.9078</v>
+        <v>-11.839</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>2.920100000000001</v>
+        <v>1.608399999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>16.7343</v>
+        <v>14.1006</v>
       </c>
       <c r="F8" t="n">
-        <v>-13.8138</v>
+        <v>-12.4918</v>
       </c>
       <c r="G8" t="n">
         <v>-5.398699999999999</v>
@@ -1078,13 +1078,13 @@
         <v>18.8934</v>
       </c>
       <c r="S8" t="n">
-        <v>7.8729</v>
+        <v>6.561199999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>5.1097</v>
+        <v>2.4763</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7632</v>
+        <v>4.085</v>
       </c>
       <c r="V8" t="n">
         <v>-5.0172</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5413</v>
+        <v>0.6354</v>
       </c>
       <c r="E9" t="n">
         <v>0.0048</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5365</v>
+        <v>0.6306</v>
       </c>
       <c r="G9" t="n">
         <v>0.8641</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3228</v>
+        <v>-0.2287</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2531</v>
+        <v>-0.159</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.539</v>
+        <v>-1.9814</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3665</v>
+        <v>-0.8403</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1725</v>
+        <v>-1.1411</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0337</v>
@@ -1234,13 +1234,13 @@
         <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4947</v>
+        <v>0.0523</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7199</v>
+        <v>0.2462</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2252</v>
+        <v>-0.1939</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0895</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.891999999999999</v>
+        <v>-7.365999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>4.299399999999999</v>
+        <v>-8.133000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.191</v>
+        <v>0.7668999999999997</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.377699999999999</v>
+        <v>-33.7958</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1283000000000001</v>
+        <v>-8.773300000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.249499999999999</v>
+        <v>-25.0227</v>
       </c>
       <c r="J11" t="n">
-        <v>16.4735</v>
+        <v>0.01709999999999867</v>
       </c>
       <c r="K11" t="n">
-        <v>7.797400000000001</v>
+        <v>8.3635</v>
       </c>
       <c r="L11" t="n">
-        <v>8.676299999999999</v>
+        <v>-8.346499999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-22.8511</v>
+        <v>-33.8128</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.925300000000001</v>
+        <v>-17.1364</v>
       </c>
       <c r="O11" t="n">
-        <v>-14.9256</v>
+        <v>-16.676</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2763</v>
+        <v>17.3001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-30.0474</v>
+        <v>-19.121</v>
       </c>
       <c r="R11" t="n">
-        <v>32.3237</v>
+        <v>36.4212</v>
       </c>
       <c r="S11" t="n">
-        <v>27.8688</v>
+        <v>9.9412</v>
       </c>
       <c r="T11" t="n">
-        <v>17.0396</v>
+        <v>1.5231</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8291</v>
+        <v>8.418100000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-25.6593</v>
+        <v>-0.8113999999999997</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8337000000000001</v>
+        <v>9.4483</v>
       </c>
       <c r="X11" t="n">
-        <v>-26.4927</v>
+        <v>-10.2597</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.014799999999999</v>
+        <v>-10.5373</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.927299999999999</v>
+        <v>-11.7308</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9128000000000006</v>
+        <v>1.193800000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-33.7958</v>
+        <v>-5.4259</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.773300000000001</v>
+        <v>-10.5419</v>
       </c>
       <c r="I12" t="n">
-        <v>-25.0227</v>
+        <v>5.1155</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01709999999999867</v>
+        <v>19.2398</v>
       </c>
       <c r="K12" t="n">
-        <v>8.3635</v>
+        <v>3.7987</v>
       </c>
       <c r="L12" t="n">
-        <v>-8.346499999999999</v>
+        <v>15.4412</v>
       </c>
       <c r="M12" t="n">
-        <v>-33.8128</v>
+        <v>-24.6656</v>
       </c>
       <c r="N12" t="n">
-        <v>-17.1364</v>
+        <v>-14.3401</v>
       </c>
       <c r="O12" t="n">
-        <v>-16.676</v>
+        <v>-10.3253</v>
       </c>
       <c r="P12" t="n">
-        <v>17.3001</v>
+        <v>-2.276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-19.121</v>
+        <v>-50.7618</v>
       </c>
       <c r="R12" t="n">
-        <v>36.4212</v>
+        <v>48.486</v>
       </c>
       <c r="S12" t="n">
-        <v>9.2926</v>
+        <v>7.2609</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7291000000000006</v>
+        <v>-1.1677</v>
       </c>
       <c r="U12" t="n">
-        <v>8.563800000000001</v>
+        <v>8.4285</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8113999999999997</v>
+        <v>-10.0954</v>
       </c>
       <c r="W12" t="n">
-        <v>9.4483</v>
+        <v>20.9592</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.2597</v>
+        <v>-31.0545</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>X. CASTANEDA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.6382</v>
+        <v>-16.2771</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.8912</v>
+        <v>-15.873</v>
       </c>
       <c r="F13" t="n">
-        <v>3.252799999999999</v>
+        <v>-0.4039000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.4259</v>
+        <v>-12.0653</v>
       </c>
       <c r="H13" t="n">
-        <v>-10.5419</v>
+        <v>-7.1912</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1155</v>
+        <v>-4.8741</v>
       </c>
       <c r="J13" t="n">
-        <v>19.2398</v>
+        <v>-8.0282</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7987</v>
+        <v>-5.1073</v>
       </c>
       <c r="L13" t="n">
-        <v>15.4412</v>
+        <v>-2.9208</v>
       </c>
       <c r="M13" t="n">
-        <v>-24.6656</v>
+        <v>-4.0369</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.3401</v>
+        <v>-2.0838</v>
       </c>
       <c r="O13" t="n">
-        <v>-10.3253</v>
+        <v>-1.9532</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.276</v>
+        <v>-5.2355</v>
       </c>
       <c r="Q13" t="n">
-        <v>-50.7618</v>
+        <v>-8.4224</v>
       </c>
       <c r="R13" t="n">
-        <v>48.486</v>
+        <v>3.1869</v>
       </c>
       <c r="S13" t="n">
-        <v>7.159699999999999</v>
+        <v>-0.1372</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.3283</v>
+        <v>-0.6698</v>
       </c>
       <c r="U13" t="n">
-        <v>10.488</v>
+        <v>0.5325</v>
       </c>
       <c r="V13" t="n">
-        <v>-10.0954</v>
+        <v>1.1608</v>
       </c>
       <c r="W13" t="n">
-        <v>20.9592</v>
+        <v>1.2472</v>
       </c>
       <c r="X13" t="n">
-        <v>-31.0545</v>
+        <v>-0.08640000000000003</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X. CASTANEDA</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.5988</v>
+        <v>-17.3056</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.3469</v>
+        <v>-19.6295</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.252</v>
+        <v>2.3237</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.0653</v>
+        <v>-8.103199999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.1912</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.8741</v>
+        <v>-16.2133</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.0282</v>
+        <v>11.0903</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.1073</v>
+        <v>16.2375</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.9208</v>
+        <v>-5.147600000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.0369</v>
+        <v>-19.1932</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0838</v>
+        <v>-8.127700000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9532</v>
+        <v>-11.0655</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.2355</v>
+        <v>-5.2356</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.4224</v>
+        <v>-37.7869</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1869</v>
+        <v>32.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.459</v>
+        <v>-0.3323999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1435</v>
+        <v>-1.6069</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3156</v>
+        <v>1.2747</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1608</v>
+        <v>-3.6344</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2472</v>
+        <v>8.674300000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.08640000000000003</v>
+        <v>-12.3087</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.7618</v>
+        <v>-18.5861</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.2561</v>
+        <v>-6.848299999999998</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.5055</v>
+        <v>-11.7373</v>
       </c>
       <c r="G15" t="n">
-        <v>-18.184</v>
+        <v>-6.377699999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.0905</v>
+        <v>-0.1283000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-8.0936</v>
+        <v>-6.249499999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.691499999999999</v>
+        <v>16.4735</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.4398</v>
+        <v>7.797400000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7479000000000005</v>
+        <v>8.676299999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-16.4925</v>
+        <v>-22.8511</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.651</v>
+        <v>-7.925300000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.841699999999999</v>
+        <v>-14.9256</v>
       </c>
       <c r="P15" t="n">
-        <v>3.869699999999999</v>
+        <v>2.2763</v>
       </c>
       <c r="Q15" t="n">
-        <v>-23.9013</v>
+        <v>-30.0474</v>
       </c>
       <c r="R15" t="n">
-        <v>27.771</v>
+        <v>32.3237</v>
       </c>
       <c r="S15" t="n">
-        <v>11.147</v>
+        <v>11.1748</v>
       </c>
       <c r="T15" t="n">
-        <v>10.1429</v>
+        <v>5.8921</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0045</v>
+        <v>5.2826</v>
       </c>
       <c r="V15" t="n">
-        <v>-14.5943</v>
+        <v>-25.6593</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1938</v>
+        <v>0.8337000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-16.7881</v>
+        <v>-26.4927</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-21.4609</v>
+        <v>-20.4626</v>
       </c>
       <c r="E16" t="n">
-        <v>-23.2179</v>
+        <v>-11.1669</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7572</v>
+        <v>-9.2957</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.103199999999999</v>
+        <v>-7.7577</v>
       </c>
       <c r="H16" t="n">
-        <v>8.110099999999999</v>
+        <v>-3.0763</v>
       </c>
       <c r="I16" t="n">
-        <v>-16.2133</v>
+        <v>-4.681300000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>11.0903</v>
+        <v>10.5593</v>
       </c>
       <c r="K16" t="n">
-        <v>16.2375</v>
+        <v>6.658199999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-5.147600000000001</v>
+        <v>3.901</v>
       </c>
       <c r="M16" t="n">
-        <v>-19.1932</v>
+        <v>-18.3172</v>
       </c>
       <c r="N16" t="n">
-        <v>-8.127700000000001</v>
+        <v>-9.734999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.0655</v>
+        <v>-8.5822</v>
       </c>
       <c r="P16" t="n">
-        <v>-5.2356</v>
+        <v>2.7316</v>
       </c>
       <c r="Q16" t="n">
-        <v>-37.7869</v>
+        <v>-23.6739</v>
       </c>
       <c r="R16" t="n">
-        <v>32.5515</v>
+        <v>26.4057</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.4879</v>
+        <v>2.4735</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.1955</v>
+        <v>0.212</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7077999999999999</v>
+        <v>2.2612</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.6344</v>
+        <v>-17.9099</v>
       </c>
       <c r="W16" t="n">
-        <v>8.674300000000001</v>
+        <v>1.7354</v>
       </c>
       <c r="X16" t="n">
-        <v>-12.3087</v>
+        <v>-19.6456</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. KRAVISH</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-24.4456</v>
+        <v>-23.3588</v>
       </c>
       <c r="E17" t="n">
-        <v>-23.0436</v>
+        <v>-19.234</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4021</v>
+        <v>-4.1248</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.1452</v>
+        <v>-18.184</v>
       </c>
       <c r="H17" t="n">
-        <v>-7.1365</v>
+        <v>-10.0905</v>
       </c>
       <c r="I17" t="n">
-        <v>-8.0084</v>
+        <v>-8.0936</v>
       </c>
       <c r="J17" t="n">
-        <v>-6.8368</v>
+        <v>-1.691499999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.4734</v>
+        <v>-2.4398</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.3634</v>
+        <v>0.7479000000000005</v>
       </c>
       <c r="M17" t="n">
-        <v>-8.308299999999999</v>
+        <v>-16.4925</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.6632</v>
+        <v>-7.651</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.6451</v>
+        <v>-8.841699999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-8.194700000000001</v>
+        <v>3.869699999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-20.0316</v>
+        <v>-23.9013</v>
       </c>
       <c r="R17" t="n">
-        <v>11.8369</v>
+        <v>27.771</v>
       </c>
       <c r="S17" t="n">
-        <v>2.977300000000001</v>
+        <v>5.5502</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7859</v>
+        <v>4.165</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1913</v>
+        <v>1.3847</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.0829</v>
+        <v>-14.5943</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0393</v>
+        <v>2.1938</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.1221</v>
+        <v>-16.7881</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>D. KRAVISH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>-26.8477</v>
+        <v>-25.528</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.4629</v>
+        <v>-23.8793</v>
       </c>
       <c r="F18" t="n">
-        <v>-14.3851</v>
+        <v>-1.6486</v>
       </c>
       <c r="G18" t="n">
-        <v>-7.7577</v>
+        <v>-15.1452</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.0763</v>
+        <v>-7.1365</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.681300000000001</v>
+        <v>-8.0084</v>
       </c>
       <c r="J18" t="n">
-        <v>10.5593</v>
+        <v>-6.8368</v>
       </c>
       <c r="K18" t="n">
-        <v>6.658199999999999</v>
+        <v>-4.4734</v>
       </c>
       <c r="L18" t="n">
-        <v>3.901</v>
+        <v>-2.3634</v>
       </c>
       <c r="M18" t="n">
-        <v>-18.3172</v>
+        <v>-8.308299999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-9.734999999999999</v>
+        <v>-2.6632</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.5822</v>
+        <v>-5.6451</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7316</v>
+        <v>-8.194700000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-23.6739</v>
+        <v>-20.0316</v>
       </c>
       <c r="R18" t="n">
-        <v>26.4057</v>
+        <v>11.8369</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.9114</v>
+        <v>1.8947</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0839</v>
+        <v>-0.05020000000000008</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.8276</v>
+        <v>1.9449</v>
       </c>
       <c r="V18" t="n">
-        <v>-17.9099</v>
+        <v>-4.0829</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7354</v>
+        <v>3.0393</v>
       </c>
       <c r="X18" t="n">
-        <v>-19.6456</v>
+        <v>-7.1221</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>-39.9562</v>
+        <v>-30.5165</v>
       </c>
       <c r="E19" t="n">
-        <v>-23.9947</v>
+        <v>-18.8939</v>
       </c>
       <c r="F19" t="n">
-        <v>-15.9615</v>
+        <v>-11.6218</v>
       </c>
       <c r="G19" t="n">
         <v>-30.7421</v>
@@ -1936,13 +1936,13 @@
         <v>44.8436</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0704</v>
+        <v>10.5106</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4275</v>
+        <v>3.6727</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4981</v>
+        <v>6.8378</v>
       </c>
       <c r="V19" t="n">
         <v>-23.0319</v>
@@ -1969,22 +1969,22 @@
         <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>-26.67260000000001</v>
+        <v>-2.166599999999995</v>
       </c>
       <c r="E20" t="n">
-        <v>31.47000000000001</v>
+        <v>40.18289999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-58.14100000000001</v>
+        <v>-42.3474</v>
       </c>
       <c r="G20" t="n">
-        <v>-35.9856</v>
+        <v>-35.98560000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-28.2782</v>
+        <v>-28.27820000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-7.707599999999999</v>
+        <v>-7.707599999999998</v>
       </c>
       <c r="J20" t="n">
         <v>291.3557</v>
@@ -2011,19 +2011,19 @@
         <v>-479.1656</v>
       </c>
       <c r="R20" t="n">
-        <v>500.7921</v>
+        <v>500.7920999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>61.0969</v>
+        <v>85.604</v>
       </c>
       <c r="T20" t="n">
-        <v>3.174499999999998</v>
+        <v>11.8862</v>
       </c>
       <c r="U20" t="n">
-        <v>57.92450000000001</v>
+        <v>73.71680000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-73.4079</v>
+        <v>-73.40789999999998</v>
       </c>
       <c r="W20" t="n">
         <v>216.1068</v>
